--- a/src/test/java/TestData/TestData.xlsx
+++ b/src/test/java/TestData/TestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Junit5Cucumber\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8808AC-2D2F-40EC-BB55-D793A27ECB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453E6E04-6FE4-47E9-AF43-FDB6FA878ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C2485C87-14CA-4D77-BFBC-C5EEDECF6FD8}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>UserName</t>
   </si>
@@ -37,6 +37,18 @@
   </si>
   <si>
     <t>DarshanKA47@</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Sign in or create account</t>
+  </si>
+  <si>
+    <t>Carturl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/gp/cart/view.html?ref_=nav_cart</t>
   </si>
 </sst>
 </file>
@@ -410,34 +422,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F67611C0-5512-4BA4-BA4B-50AF69EB3A6A}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{3775EB09-CAA0-4433-B22B-4CB86FFD1985}"/>
     <hyperlink ref="B2" r:id="rId2" xr:uid="{FE53E94E-2366-4046-9DC9-654711449DC6}"/>
+    <hyperlink ref="D2" r:id="rId3" xr:uid="{08179342-9792-4EA9-9BB6-EC7FDD1C2C56}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>